--- a/082626_20pc_LT_Cluster10_GUM.xlsx
+++ b/082626_20pc_LT_Cluster10_GUM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ATDI\Rodney\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71805B57-6A7F-4EB8-83E1-183464C68CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB1FF540-3C84-45B8-B947-48292D532E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="210" windowWidth="18340" windowHeight="10240" xr2:uid="{D052E148-F1A0-4AA5-A65C-E0D5632B9B5B}"/>
+    <workbookView xWindow="20" yWindow="210" windowWidth="18340" windowHeight="10240" xr2:uid="{93F19C18-E549-43DA-BD4A-E6A8B154DB81}"/>
   </bookViews>
   <sheets>
     <sheet name="jtemp1000_130" sheetId="1" r:id="rId1"/>
@@ -1085,7 +1085,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4ECEA40-EBAA-4631-9126-59A9F170E928}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADDA8E00-0776-4F70-A1C0-8D9277FE1731}">
   <dimension ref="A1:AP33"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
@@ -5314,7 +5314,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP1" xr:uid="{A4ECEA40-EBAA-4631-9126-59A9F170E928}"/>
+  <autoFilter ref="A1:AP1" xr:uid="{ADDA8E00-0776-4F70-A1C0-8D9277FE1731}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>